--- a/Docs/Ke_hoach_Do_an_Inventory_Microservice.xlsx
+++ b/Docs/Ke_hoach_Do_an_Inventory_Microservice.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">KẾ HOẠCH ĐỒ ÁN: INVENTORY MICROSERVICE (tên tạm)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dựa trên SRS TigerNet v1.1 · lập ngày 25/10/2026 · các ô nền vàng là ô cần điền/cập nhật</t>
+    <t xml:space="preserve">Dựa trên SRS TigerNet v1.1 · lập 25/10/2026, chuyển backend sang Java Spring Boot 26/10/2026 · các ô nền vàng là ô cần điền/cập nhật</t>
   </si>
   <si>
     <t xml:space="preserve">Tên dự án</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Backend</t>
   </si>
   <si>
-    <t xml:space="preserve">NodeJS 22 · Express · Prisma · MySQL 8 (database per service) · Redis · RabbitMQ · Socket.IO · Jest</t>
+    <t xml:space="preserve">Java 21 · Spring Boot 3.3 · Spring Cloud (Gateway, Eureka, OpenFeign) · Spring Data JPA + Flyway · Spring Security + JWT · MySQL 8 (database per service) · Redis (Redisson) · RabbitMQ (Spring AMQP) · WebSocket STOMP · JUnit 5 + Testcontainers · Maven multi-module</t>
   </si>
   <si>
     <t xml:space="preserve">Frontend</t>
@@ -88,13 +88,13 @@
     <t xml:space="preserve">Hạ tầng</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker Compose (dev + demo) · GitHub Actions CI · deploy VPS/Render khi bàn giao</t>
+    <t xml:space="preserve">Docker Compose (MySQL, Redis, RabbitMQ, MailHog, Zipkin) · GitHub Actions CI · deploy VPS khi bàn giao</t>
   </si>
   <si>
     <t xml:space="preserve">Services</t>
   </si>
   <si>
-    <t xml:space="preserve">api-gateway · auth-service · catalog-service · inventory-service · order-service · report-service</t>
+    <t xml:space="preserve">discovery-server (Eureka) · api-gateway (Spring Cloud Gateway) · auth-service · catalog-service · inventory-service · order-service · report-service</t>
   </si>
   <si>
     <t xml:space="preserve">Phạm vi KHÔNG làm</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Backend 1 + DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">packages/common, api-gateway, auth-service, catalog-service, report-service (báo cáo, cảnh báo, audit, xuất file, backup), thanh toán/công nợ, CI/CD, deploy</t>
+    <t xml:space="preserve">common-lib, discovery-server (Eureka), api-gateway, auth-service, catalog-service, report-service (báo cáo, cảnh báo, audit, xuất file, backup), thanh toán/công nợ, CI/CD, deploy</t>
   </si>
   <si>
     <t xml:space="preserve">PR của Quân</t>
@@ -184,7 +184,7 @@
     <t xml:space="preserve">26/10 – 08/11</t>
   </si>
   <si>
-    <t xml:space="preserve">Nền tảng: repo, docker, CSDL, common lib, gateway, đăng nhập, kho; Figma design system + wireframe; FE khung app</t>
+    <t xml:space="preserve">Nền tảng: repo Maven, docker, CSDL (Flyway), common-lib, Eureka + gateway, đăng nhập, kho; Figma design system + wireframe; FE khung app</t>
   </si>
   <si>
     <t xml:space="preserve">v0.1.0</t>
@@ -298,16 +298,16 @@
     <t xml:space="preserve">FE phải sửa nhiều</t>
   </si>
   <si>
-    <t xml:space="preserve">Chốt OpenAPI W2; đổi contract phải có FE approve PR; dùng mock (MSW) khi BE chưa xong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microservice khó debug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mất thời gian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log có request-id xuyên service (pino), docker compose 1 lệnh, health check mỗi service</t>
+    <t xml:space="preserve">Chốt OpenAPI W2; đổi contract phải có FE approve PR; dùng mock (MSW) khi BE chưa xong; springdoc sinh OpenAPI tự động</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhóm chưa quen Spring Cloud / boilerplate Java nhiều</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chậm tiến độ Sprint 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dùng Spring Initializr + Lombok + MapStruct; Nhật dựng sẵn common-lib và 1 service mẫu ở W1 cho Quân làm theo; Micrometer Tracing (traceId xuyên service) + Zipkin, Actuator health, docker compose 1 lệnh</t>
   </si>
   <si>
     <t xml:space="preserve">KẾ HOẠCH 9 TUẦN &amp; CHIA VIỆC</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">Quản lý</t>
   </si>
   <si>
-    <t xml:space="preserve">Kick-off, đọc SRS v1.1, chốt phạm vi MVP, tạo GitHub Project &amp; issue từ sheet này</t>
+    <t xml:space="preserve">Kick-off, đọc SRS v1.1, chốt phạm vi MVP, cài môi trường (JDK 21, IntelliJ, Docker, Node 22 cho FE), tạo GitHub Project &amp; issue từ sheet này</t>
   </si>
   <si>
     <t xml:space="preserve">Cả nhóm</t>
@@ -418,7 +418,7 @@
     <t xml:space="preserve">DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Tạo monorepo (npm workspaces), ESLint/Prettier, husky + commitlint, PR template, CODEOWNERS, branch protection</t>
+    <t xml:space="preserve">Tạo repo: Backend/ (Maven parent pom, Java 21, Spring Boot 3.3, Spotless + Checkstyle), Frontend/, Docs/; PR template, CODEOWNERS, branch protection; kiểm tên PR theo Conventional Commits</t>
   </si>
   <si>
     <t xml:space="preserve">Repo + quy ước</t>
@@ -430,10 +430,10 @@
     <t xml:space="preserve">Database</t>
   </si>
   <si>
-    <t xml:space="preserve">Review &amp; chốt ERD + schema.sql 5 database; Prisma schema + migration + seed cho từng service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">schema.prisma ×5, seed</t>
+    <t xml:space="preserve">Review &amp; chốt ERD + schema.sql 5 database; tách thành Flyway migration V1__init.sql + V2__seed.sql cho từng service; JPA entity mẫu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flyway ×5, seed</t>
   </si>
   <si>
     <t xml:space="preserve">T04</t>
@@ -451,10 +451,10 @@
     <t xml:space="preserve">Backend chung</t>
   </si>
   <si>
-    <t xml:space="preserve">packages/common: logger(pino, request-id), AppError, errorHandler, response, validate(zod), auth-context, requireRole, requireWarehouseAccess, rabbitmq, httpClient, idempotency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inv/common</t>
+    <t xml:space="preserve">common-lib (Maven module): ApiResponse, BusinessException + @RestControllerAdvice, JWT filter + UserContext, @RequireWarehouseAccess (AOP), AMQP config + event DTO, Feign interceptor (X-Internal-Key, traceId), IdempotencyService; 1 service mẫu (catalog skeleton)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common-lib + service mẫu</t>
   </si>
   <si>
     <t xml:space="preserve">T06</t>
@@ -472,7 +472,7 @@
     <t xml:space="preserve">T07</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub Actions CI: lint + test + build theo service (paths filter)</t>
+    <t xml:space="preserve">GitHub Actions CI: mvn verify (Spotless, Checkstyle, JUnit, Testcontainers) theo module bị đổi + build FE (Vite)</t>
   </si>
   <si>
     <t xml:space="preserve">ci.yml xanh</t>
@@ -484,13 +484,13 @@
     <t xml:space="preserve">Gateway</t>
   </si>
   <si>
-    <t xml:space="preserve">api-gateway: proxy 5 service, verify JWT, gắn header user/kho, rate limit theo user/ngày, CORS, gộp Swagger, proxy WebSocket</t>
+    <t xml:space="preserve">discovery-server (Eureka :8761) + api-gateway (Spring Cloud Gateway): route 5 service qua lb://, filter verify JWT, gắn header user/kho, RequestRateLimiter (Redis) theo user, CORS, gộp Swagger UI, route WebSocket</t>
   </si>
   <si>
     <t xml:space="preserve">common</t>
   </si>
   <si>
-    <t xml:space="preserve">Gateway :8080</t>
+    <t xml:space="preserve">Gateway :8080 + Eureka</t>
   </si>
   <si>
     <t xml:space="preserve">T09</t>
@@ -499,7 +499,7 @@
     <t xml:space="preserve">Auth</t>
   </si>
   <si>
-    <t xml:space="preserve">auth-service: login, refresh, logout, me; bcrypt; khóa 5 phút sau 5 lần sai; login_histories</t>
+    <t xml:space="preserve">auth-service: Spring Security, login, refresh, logout, me; BCryptPasswordEncoder; khóa 5 phút sau 5 lần sai; login_histories</t>
   </si>
   <si>
     <t xml:space="preserve">API Auth P0</t>
@@ -595,7 +595,7 @@
     <t xml:space="preserve">Sprint 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Quên mật khẩu OTP qua email (nodemailer/MailHog), đổi mật khẩu</t>
+    <t xml:space="preserve">Quên mật khẩu OTP qua email (Spring Mail + MailHog khi dev, OTP lưu Redis TTL), đổi mật khẩu</t>
   </si>
   <si>
     <t xml:space="preserve">Auth P0</t>
@@ -631,7 +631,7 @@
     <t xml:space="preserve">T20</t>
   </si>
   <si>
-    <t xml:space="preserve">Lõi tồn kho: stock_balances, stock_items, stock_movements; API nội bộ receive/check/reserve/commit/release với transaction + SELECT FOR UPDATE + version + Redis lock + Idempotency-Key</t>
+    <t xml:space="preserve">Lõi tồn kho: entity StockBalance (@Version), StockItem, StockMovement; API nội bộ receive/check/reserve/commit/release với @Transactional + @Lock(PESSIMISTIC_WRITE) + Redisson lock + Idempotency-Key</t>
   </si>
   <si>
     <t xml:space="preserve">Internal stock API</t>
@@ -646,7 +646,7 @@
     <t xml:space="preserve">Lõi tồn</t>
   </si>
   <si>
-    <t xml:space="preserve">Jest test</t>
+    <t xml:space="preserve">JUnit + Testcontainers</t>
   </si>
   <si>
     <t xml:space="preserve">T22</t>
@@ -655,7 +655,7 @@
     <t xml:space="preserve">Order</t>
   </si>
   <si>
-    <t xml:space="preserve">order-service: doc_sequences sinh mã, phiếu nhập CRUD + xác nhận → cộng tồn kho nhận, kiểm serial trùng toàn hệ thống, outbox publisher</t>
+    <t xml:space="preserve">order-service: doc_sequences sinh mã, phiếu nhập CRUD + xác nhận → gọi inventory qua OpenFeign (Resilience4j retry), kiểm serial trùng toàn hệ thống, outbox publisher (@Scheduled)</t>
   </si>
   <si>
     <t xml:space="preserve">API Receipts</t>
@@ -676,7 +676,7 @@
     <t xml:space="preserve">Report</t>
   </si>
   <si>
-    <t xml:space="preserve">report-service khung: consumer RabbitMQ, audit log, notifications API + Socket.IO qua gateway</t>
+    <t xml:space="preserve">report-service khung: @RabbitListener consumer, audit log, notifications API + WebSocket STOMP (/ws, /topic/notifications) qua gateway</t>
   </si>
   <si>
     <t xml:space="preserve">RabbitMQ</t>
@@ -793,7 +793,7 @@
     <t xml:space="preserve">T35</t>
   </si>
   <si>
-    <t xml:space="preserve">Cảnh báo: cron + event (tồn dưới ngưỡng, sắp hết hạn thuê/mượn, phiếu chờ duyệt lâu, chuyển kho quá hạn/sai lệch, giữ hàng sắp hết hạn, công nợ quá hạn) theo phạm vi kho</t>
+    <t xml:space="preserve">Cảnh báo: @Scheduled + ShedLock + event (tồn dưới ngưỡng, sắp hết hạn thuê/mượn, phiếu chờ duyệt lâu, chuyển kho quá hạn/sai lệch, giữ hàng sắp hết hạn, công nợ quá hạn) theo phạm vi kho</t>
   </si>
   <si>
     <t xml:space="preserve">Notifications</t>
@@ -889,7 +889,7 @@
     <t xml:space="preserve">Kiểm thử</t>
   </si>
   <si>
-    <t xml:space="preserve">Integration test 10 kịch bản SRS 8.5 (đa kho) + test phân quyền kho gọi API trực tiếp</t>
+    <t xml:space="preserve">Integration test (Spring Boot Test + Testcontainers MySQL/Redis/RabbitMQ) 10 kịch bản SRS 8.5 (đa kho) + test phân quyền kho gọi API trực tiếp</t>
   </si>
   <si>
     <t xml:space="preserve">Tất cả API</t>
@@ -913,7 +913,7 @@
     <t xml:space="preserve">T46</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất file Excel (ExcelJS) / PDF (PDFKit) qua export job; backup mysqldump tự động hằng ngày + thủ công; API audit log</t>
+    <t xml:space="preserve">Xuất file Excel (Apache POI) / PDF (OpenPDF hoặc JasperReports) qua export job @Async; backup mysqldump (container cron) hằng ngày + thủ công; API audit log</t>
   </si>
   <si>
     <t xml:space="preserve">Export + Backup</t>
@@ -985,7 +985,7 @@
     <t xml:space="preserve">T52</t>
   </si>
   <si>
-    <t xml:space="preserve">Deploy demo (VPS/Render + docker compose), seed dữ liệu demo 3 kho, HTTPS</t>
+    <t xml:space="preserve">Deploy demo (VPS + docker compose, image build bằng Jib/Dockerfile), seed dữ liệu demo 3 kho, HTTPS</t>
   </si>
   <si>
     <t xml:space="preserve">URL demo</t>
@@ -1411,7 +1411,7 @@
     <t xml:space="preserve">/api/v1/products/:id/image</t>
   </si>
   <si>
-    <t xml:space="preserve">Upload ảnh sản phẩm (multer)</t>
+    <t xml:space="preserve">Upload ảnh sản phẩm (MultipartFile)</t>
   </si>
   <si>
     <t xml:space="preserve">/api/v1/products/export</t>
@@ -1468,7 +1468,7 @@
     <t xml:space="preserve">WS</t>
   </si>
   <si>
-    <t xml:space="preserve">WS /socket.io  (event: notification:new)</t>
+    <t xml:space="preserve">WS /ws  (STOMP, subscribe /user/queue/notifications)</t>
   </si>
   <si>
     <t xml:space="preserve">Đẩy cảnh báo realtime qua gateway</t>
@@ -2965,7 +2965,7 @@
     <t xml:space="preserve">Cấu hình, CI, docker, version</t>
   </si>
   <si>
-    <t xml:space="preserve">ci: cache npm theo workspace</t>
+    <t xml:space="preserve">ci: cache Maven ~/.m2 theo module</t>
   </si>
   <si>
     <t xml:space="preserve">Scope</t>
@@ -2974,7 +2974,7 @@
     <t xml:space="preserve">auth · catalog · inventory · order · report · gateway · common · fe · infra · docs</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiểm bằng commitlint + husky (commit-msg hook)</t>
+    <t xml:space="preserve">Kiểm tên PR bằng GitHub Action (amannn/action-semantic-pull-request); khuyến khích dùng plugin Conventional Commits trong IntelliJ</t>
   </si>
   <si>
     <t xml:space="preserve">3. PULL REQUEST</t>
@@ -2998,7 +2998,7 @@
     <t xml:space="preserve">2. Code + test</t>
   </si>
   <si>
-    <t xml:space="preserve">Commit nhỏ, đúng chuẩn; chạy npm run lint &amp;&amp; npm test</t>
+    <t xml:space="preserve">Commit nhỏ, đúng chuẩn; backend chạy mvn -pl &lt;module&gt; -am verify, frontend chạy npm run lint &amp;&amp; npm test</t>
   </si>
   <si>
     <t xml:space="preserve">Đổi API → cập nhật OpenAPI trong cùng PR</t>
@@ -3100,7 +3100,7 @@
     <t xml:space="preserve">CODEOWNERS</t>
   </si>
   <si>
-    <t xml:space="preserve">services/auth-service, catalog-service, report-service, api-gateway, packages → Nhật; inventory-service, order-service, infra → Quân; frontend → Nghĩa</t>
+    <t xml:space="preserve">Backend/auth-service, catalog-service, report-service, api-gateway, discovery-server, common-lib → Nhật; Backend/inventory-service, order-service, infra → Quân; Frontend/ → Nghĩa</t>
   </si>
   <si>
     <t xml:space="preserve">Tự gán reviewer</t>
@@ -3109,7 +3109,7 @@
     <t xml:space="preserve">CI (GitHub Actions)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mỗi PR: npm ci → lint → test (MySQL/Redis service container) → build; chỉ chạy service bị thay đổi</t>
+    <t xml:space="preserve">Mỗi PR: mvn verify (Spotless, Checkstyle, JUnit, Testcontainers) cho module bị đổi; Frontend: npm ci → lint → test → build</t>
   </si>
   <si>
     <t xml:space="preserve">.github/workflows/ci.yml</t>
@@ -3944,7 +3944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>85</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>974</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>983</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
         <v>1017</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
         <v>1020</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
         <v>114</v>
       </c>
@@ -4869,7 +4869,7 @@
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
@@ -5004,7 +5004,7 @@
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
     </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>133</v>
       </c>
@@ -5094,7 +5094,7 @@
       <c r="T10" s="16"/>
       <c r="U10" s="16"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
         <v>141</v>
       </c>
@@ -5139,7 +5139,7 @@
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>144</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>119</v>
@@ -5558,7 +5558,7 @@
       <c r="T20" s="16"/>
       <c r="U20" s="16"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
         <v>181</v>
       </c>
@@ -5699,7 +5699,7 @@
       <c r="T23" s="16"/>
       <c r="U23" s="16"/>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
         <v>194</v>
       </c>
@@ -5793,7 +5793,7 @@
       <c r="T25" s="16"/>
       <c r="U25" s="16"/>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>201</v>
       </c>
@@ -5887,7 +5887,7 @@
       <c r="T27" s="16"/>
       <c r="U27" s="16"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
         <v>208</v>
       </c>
@@ -6823,7 +6823,7 @@
       <c r="T47" s="16"/>
       <c r="U47" s="16"/>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
         <v>279</v>
       </c>
@@ -6917,7 +6917,7 @@
       <c r="T49" s="16"/>
       <c r="U49" s="16"/>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
         <v>288</v>
       </c>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">SUMPRODUCT((('Kế hoạch &amp; Chia việc'!$E$5:$E$58="Nhật")+('Kế hoạch &amp; Chia việc'!$E$5:$E$58="Cả nhóm"))*('Kế hoạch &amp; Chia việc'!$F$5:$F$58&lt;=2)*('Kế hoạch &amp; Chia việc'!$G$5:$G$58&gt;=2)*'Kế hoạch &amp; Chia việc'!$H$5:$H$58/('Kế hoạch &amp; Chia việc'!$G$5:$G$58-'Kế hoạch &amp; Chia việc'!$F$5:$F$58+1))</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">SUMPRODUCT((('Kế hoạch &amp; Chia việc'!$E$5:$E$58="Nhật")+('Kế hoạch &amp; Chia việc'!$E$5:$E$58="Cả nhóm"))*('Kế hoạch &amp; Chia việc'!$F$5:$F$58&lt;=3)*('Kế hoạch &amp; Chia việc'!$G$5:$G$58&gt;=3)*'Kế hoạch &amp; Chia việc'!$H$5:$H$58/('Kế hoạch &amp; Chia việc'!$G$5:$G$58-'Kế hoạch &amp; Chia việc'!$F$5:$F$58+1))</f>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="K5" s="17" t="n">
         <f aca="false">SUM(B5:J5)</f>
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L5" s="13" t="n">
         <f aca="false">COUNTIF('Kế hoạch &amp; Chia việc'!$E$5:$E$58,"Nhật")+COUNTIF('Kế hoạch &amp; Chia việc'!$E$5:$E$58,"Cả nhóm")</f>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">SUM(C5:C7)</f>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">SUM(D5:D7)</f>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="K8" s="20" t="n">
         <f aca="false">SUM(K5:K7)</f>
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L8" s="21" t="n">
         <f aca="false">SUM(L5:L7)</f>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="n">
         <v>53</v>
       </c>
@@ -15479,7 +15479,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="n">
         <v>63</v>
       </c>
